--- a/sheets/Libetee_増額シミュレーション.xlsx
+++ b/sheets/Libetee_増額シミュレーション.xlsx
@@ -18,10 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="165" formatCode="m/d(aaa)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -227,19 +226,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,7 +503,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1000,6 +999,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1227,6 +1227,7 @@
         <v>47586477</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
@@ -1262,6 +1263,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1410,6 +1412,7 @@
         <v>4270706</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="H8" t="inlineStr">
         <is>
@@ -1474,6 +1477,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1517,8 +1521,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="n">
-        <v>46235</v>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
@@ -1547,8 +1553,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="n">
-        <v>46236</v>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
@@ -1577,8 +1585,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="n">
-        <v>46237</v>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
@@ -1607,8 +1617,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="n">
-        <v>46238</v>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
@@ -1637,8 +1649,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="n">
-        <v>46239</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -1667,8 +1681,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="n">
-        <v>46240</v>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
@@ -1697,8 +1713,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="n">
-        <v>46241</v>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
@@ -1727,8 +1745,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="n">
-        <v>46242</v>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
@@ -1757,8 +1777,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n">
-        <v>46243</v>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -1787,8 +1809,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n">
-        <v>46244</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1817,8 +1841,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="n">
-        <v>46245</v>
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -1847,8 +1873,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="n">
-        <v>46246</v>
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
@@ -1877,8 +1905,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="n">
-        <v>46247</v>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
@@ -1907,8 +1937,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="n">
-        <v>46248</v>
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -1937,8 +1969,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="40" t="n">
-        <v>46249</v>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1967,8 +2001,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="n">
-        <v>46250</v>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
@@ -1997,8 +2033,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="37" t="n">
-        <v>46251</v>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
@@ -2027,8 +2065,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37" t="n">
-        <v>46252</v>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
@@ -2057,8 +2097,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="37" t="n">
-        <v>46253</v>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -2087,8 +2129,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="40" t="n">
-        <v>46254</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2117,8 +2161,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="n">
-        <v>46255</v>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
@@ -2147,8 +2193,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="n">
-        <v>46256</v>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
@@ -2177,8 +2225,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="n">
-        <v>46257</v>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
@@ -2207,8 +2257,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n">
-        <v>46258</v>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
@@ -2237,8 +2289,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="n">
-        <v>46259</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -2267,8 +2321,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="n">
-        <v>46260</v>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
@@ -2297,8 +2353,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="n">
-        <v>46261</v>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
@@ -2327,8 +2385,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="n">
-        <v>46262</v>
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
@@ -2357,8 +2417,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="n">
-        <v>46263</v>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
@@ -2387,8 +2449,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="n">
-        <v>46264</v>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2417,8 +2481,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="n">
-        <v>46265</v>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
